--- a/Descargas/PF-Com-Hidra.xlsx
+++ b/Descargas/PF-Com-Hidra.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sistemasmarco-my.sharepoint.com/personal/aprado_marco_com_pe/Documents/Escritorio/Rotacion Incubadoras-Electro-Frio/HIDRAULICA COMPONENTE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1055" documentId="11_AD4D2F04E46CFB4ACB3E2012DDD5DB52683EDF26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8461DDAE-AC9B-4FF5-B6BC-11F52560D6D5}"/>
+  <xr:revisionPtr revIDLastSave="1062" documentId="11_AD4D2F04E46CFB4ACB3E2012DDD5DB52683EDF26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85B88D45-BBC8-4A3A-8FB9-20EB40BC0178}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$105</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="104">
   <si>
     <t>Producto Final</t>
   </si>
@@ -80,15 +80,6 @@
     <t>A19030000378</t>
   </si>
   <si>
-    <t>A21040000051</t>
-  </si>
-  <si>
-    <t>A18130007766</t>
-  </si>
-  <si>
-    <t>A21040000050</t>
-  </si>
-  <si>
     <t>A18110000601</t>
   </si>
   <si>
@@ -96,6 +87,9 @@
   </si>
   <si>
     <t>A18110000729</t>
+  </si>
+  <si>
+    <t>A26080000018</t>
   </si>
   <si>
     <t>A18110000959</t>
@@ -823,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="6" width="16" customWidth="1"/>
@@ -930,20 +924,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
       <c r="G9" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -954,10 +948,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
         <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
       </c>
       <c r="G11" s="16">
         <v>1</v>
@@ -965,10 +959,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" s="16">
         <v>1</v>
@@ -976,10 +970,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" s="16">
         <v>1</v>
@@ -987,7 +981,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
         <v>23</v>
@@ -998,21 +992,21 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s">
         <v>24</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
         <v>25</v>
-      </c>
-      <c r="G15" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" t="s">
-        <v>26</v>
       </c>
       <c r="G16" s="16">
         <v>1</v>
@@ -1020,18 +1014,18 @@
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
         <v>27</v>
-      </c>
-      <c r="G17" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15">
-      <c r="A18" t="s">
-        <v>24</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -1042,10 +1036,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G19" s="16">
         <v>1</v>
@@ -1053,54 +1047,54 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" t="s">
         <v>29</v>
       </c>
-      <c r="F20" t="s">
-        <v>25</v>
-      </c>
       <c r="G20" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" ht="15">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15">
-      <c r="A22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" t="s">
-        <v>28</v>
-      </c>
       <c r="G22" s="16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
         <v>32</v>
       </c>
-      <c r="F23" t="s">
-        <v>33</v>
-      </c>
       <c r="G23" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G24" s="16">
         <v>2</v>
@@ -1108,10 +1102,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G25" s="16">
         <v>2</v>
@@ -1119,21 +1113,21 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G26" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" s="16">
         <v>1</v>
@@ -1141,32 +1135,32 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G28" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" t="s">
         <v>40</v>
-      </c>
-      <c r="F30" t="s">
-        <v>41</v>
       </c>
       <c r="G30" s="16">
         <v>1</v>
@@ -1174,7 +1168,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F31" t="s">
         <v>42</v>
@@ -1185,10 +1179,10 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="F32" t="s">
         <v>43</v>
-      </c>
-      <c r="F32" t="s">
-        <v>44</v>
       </c>
       <c r="G32" s="16">
         <v>1</v>
@@ -1196,9 +1190,9 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G33" s="16">
@@ -1207,10 +1201,10 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="G34" s="16">
         <v>1</v>
@@ -1218,10 +1212,10 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>46</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G35" s="16">
         <v>1</v>
@@ -1229,10 +1223,10 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>46</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="G36" s="16">
         <v>1</v>
@@ -1240,10 +1234,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="G37" s="16">
         <v>1</v>
@@ -1251,10 +1245,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="G38" s="16">
         <v>1</v>
@@ -1262,10 +1256,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>52</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="G39" s="16">
         <v>1</v>
@@ -1273,10 +1267,10 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>52</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="F40" t="s">
+        <v>51</v>
       </c>
       <c r="G40" s="16">
         <v>1</v>
@@ -1284,21 +1278,21 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>52</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="G41" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>52</v>
-      </c>
-      <c r="F42" s="4" t="s">
         <v>50</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="G42" s="16">
         <v>2</v>
@@ -1308,19 +1302,19 @@
       <c r="A43" t="s">
         <v>52</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>51</v>
+      <c r="F43" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="G43" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>54</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="G44" s="16">
         <v>1</v>
@@ -1328,10 +1322,10 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>54</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G45" s="16">
         <v>1</v>
@@ -1339,32 +1333,32 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>54</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="G46" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>54</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="G47" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="F48" t="s">
+        <v>53</v>
       </c>
       <c r="G48" s="16">
         <v>1</v>
@@ -1374,7 +1368,7 @@
       <c r="A49" t="s">
         <v>54</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G49" s="16">
@@ -1383,10 +1377,10 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F50" t="s">
         <v>56</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="G50" s="16">
         <v>1</v>
@@ -1394,31 +1388,31 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>56</v>
-      </c>
-      <c r="F51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G51" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="F52" t="s">
         <v>59</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="G52" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>59</v>
-      </c>
-      <c r="F53" t="s">
+        <v>60</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G53" s="16">
@@ -1427,10 +1421,10 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="G54" s="16">
         <v>1</v>
@@ -1438,10 +1432,10 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>62</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="G55" s="16">
         <v>1</v>
@@ -1449,10 +1443,10 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>62</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
+      </c>
+      <c r="F56" t="s">
+        <v>64</v>
       </c>
       <c r="G56" s="16">
         <v>1</v>
@@ -1460,10 +1454,10 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>62</v>
-      </c>
-      <c r="F57" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="G57" s="16">
         <v>1</v>
@@ -1471,10 +1465,10 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>62</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="G58" s="16">
         <v>1</v>
@@ -1482,10 +1476,10 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>68</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="G59" s="16">
         <v>1</v>
@@ -1493,10 +1487,10 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>68</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="F60" t="s">
+        <v>67</v>
       </c>
       <c r="G60" s="16">
         <v>1</v>
@@ -1504,21 +1498,21 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F61" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G61" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>68</v>
-      </c>
-      <c r="F62" t="s">
         <v>66</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="G62" s="16">
         <v>2</v>
@@ -1528,19 +1522,19 @@
       <c r="A63" t="s">
         <v>68</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>67</v>
+      <c r="F63" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="G63" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>70</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="G64" s="16">
         <v>1</v>
@@ -1548,10 +1542,10 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>70</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="G65" s="16">
         <v>1</v>
@@ -1559,9 +1553,9 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>70</v>
-      </c>
-      <c r="F66" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F66" s="9" t="s">
         <v>65</v>
       </c>
       <c r="G66" s="16">
@@ -1570,10 +1564,10 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>70</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="F67" t="s">
+        <v>69</v>
       </c>
       <c r="G67" s="16">
         <v>1</v>
@@ -1583,7 +1577,7 @@
       <c r="A68" t="s">
         <v>70</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="10" t="s">
         <v>71</v>
       </c>
       <c r="G68" s="16">
@@ -1592,10 +1586,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
+        <v>70</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="G69" s="16">
         <v>1</v>
@@ -1603,10 +1597,10 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>72</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="F70" t="s">
+        <v>73</v>
       </c>
       <c r="G70" s="16">
         <v>1</v>
@@ -1614,10 +1608,10 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G71" s="16">
         <v>1</v>
@@ -1625,10 +1619,10 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>72</v>
-      </c>
-      <c r="F72" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="G72" s="16">
         <v>1</v>
@@ -1636,10 +1630,10 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>72</v>
-      </c>
-      <c r="F73" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>71</v>
       </c>
       <c r="G73" s="16">
         <v>1</v>
@@ -1647,10 +1641,10 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>78</v>
-      </c>
-      <c r="F74" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="G74" s="16">
         <v>1</v>
@@ -1658,10 +1652,10 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>78</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="F75" t="s">
+        <v>73</v>
       </c>
       <c r="G75" s="16">
         <v>1</v>
@@ -1669,10 +1663,10 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G76" s="16">
         <v>1</v>
@@ -1680,10 +1674,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>78</v>
-      </c>
-      <c r="F77" t="s">
         <v>76</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="G77" s="16">
         <v>1</v>
@@ -1691,9 +1685,9 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>78</v>
-      </c>
-      <c r="F78" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F78" t="s">
         <v>77</v>
       </c>
       <c r="G78" s="16">
@@ -1704,7 +1698,7 @@
       <c r="A79" t="s">
         <v>78</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="8" t="s">
         <v>79</v>
       </c>
       <c r="G79" s="16">
@@ -1713,10 +1707,10 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
+        <v>78</v>
+      </c>
+      <c r="F80" t="s">
         <v>80</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="G80" s="16">
         <v>1</v>
@@ -1724,10 +1718,10 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>80</v>
-      </c>
-      <c r="F81" t="s">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="G81" s="16">
         <v>1</v>
@@ -1735,10 +1729,10 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>80</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>83</v>
+        <v>78</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="G82" s="16">
         <v>1</v>
@@ -1746,10 +1740,10 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>80</v>
-      </c>
-      <c r="F83" s="13" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="G83" s="16">
         <v>1</v>
@@ -1757,10 +1751,10 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>80</v>
-      </c>
-      <c r="F84" s="11" t="s">
-        <v>77</v>
+        <v>83</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="G84" s="16">
         <v>1</v>
@@ -1768,10 +1762,10 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>85</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="G85" s="16">
         <v>1</v>
@@ -1779,10 +1773,10 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>85</v>
-      </c>
-      <c r="F86" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="F86" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="G86" s="16">
         <v>1</v>
@@ -1790,10 +1784,10 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>85</v>
-      </c>
-      <c r="F87" s="12" t="s">
         <v>83</v>
+      </c>
+      <c r="F87" t="s">
+        <v>82</v>
       </c>
       <c r="G87" s="16">
         <v>1</v>
@@ -1801,10 +1795,10 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>85</v>
-      </c>
-      <c r="F88" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="G88" s="16">
         <v>1</v>
@@ -1812,10 +1806,10 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>85</v>
-      </c>
-      <c r="F89" s="15" t="s">
-        <v>77</v>
+        <v>83</v>
+      </c>
+      <c r="F89" t="s">
+        <v>84</v>
       </c>
       <c r="G89" s="16">
         <v>1</v>
@@ -1825,7 +1819,7 @@
       <c r="A90" t="s">
         <v>85</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="15" t="s">
         <v>86</v>
       </c>
       <c r="G90" s="16">
@@ -1834,10 +1828,10 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
+        <v>85</v>
+      </c>
+      <c r="F91" t="s">
         <v>87</v>
-      </c>
-      <c r="F91" s="15" t="s">
-        <v>88</v>
       </c>
       <c r="G91" s="16">
         <v>1</v>
@@ -1845,10 +1839,10 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F92" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G92" s="16">
         <v>1</v>
@@ -1856,10 +1850,10 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G93" s="16">
         <v>1</v>
@@ -1867,10 +1861,10 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>87</v>
-      </c>
-      <c r="F94" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="F94" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="G94" s="16">
         <v>1</v>
@@ -1878,10 +1872,10 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F95" s="15" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G95" s="16">
         <v>1</v>
@@ -1889,10 +1883,10 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>92</v>
-      </c>
-      <c r="F96" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+      <c r="F96" t="s">
+        <v>87</v>
       </c>
       <c r="G96" s="16">
         <v>1</v>
@@ -1900,10 +1894,10 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F97" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G97" s="16">
         <v>1</v>
@@ -1911,10 +1905,10 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F98" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G98" s="16">
         <v>1</v>
@@ -1922,10 +1916,10 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>92</v>
-      </c>
-      <c r="F99" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+      <c r="F99" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="G99" s="16">
         <v>1</v>
@@ -1933,23 +1927,23 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
+        <v>90</v>
+      </c>
+      <c r="F100" t="s">
+        <v>91</v>
+      </c>
+      <c r="G100" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F100" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="G100" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" t="s">
-        <v>92</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="F101" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G101" s="16">
+      <c r="G101" s="17">
         <v>1</v>
       </c>
     </row>
@@ -1977,10 +1971,10 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="G104" s="17">
         <v>1</v>
@@ -1988,7 +1982,7 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>100</v>
@@ -1997,43 +1991,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
-      <c r="A106" s="1" t="s">
+    <row r="106" spans="1:7" ht="15">
+      <c r="A106" t="s">
         <v>101</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="F106" t="s">
         <v>102</v>
       </c>
-      <c r="G106" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="15">
+      <c r="G106" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
+        <v>101</v>
+      </c>
+      <c r="F107" t="s">
         <v>103</v>
       </c>
-      <c r="F107" t="s">
-        <v>104</v>
-      </c>
       <c r="G107" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
-      <c r="A108" t="s">
-        <v>103</v>
-      </c>
-      <c r="F108" t="s">
-        <v>105</v>
-      </c>
-      <c r="G108" s="16">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G107" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="F1:F1048576">
+  <conditionalFormatting sqref="F1:F8 F10:F1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2218,13 +2201,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25651C27-2391-40F9-B17A-76880245B5A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7646628-9B27-4C62-8F03-06CE67EC70B9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AA284B7-56E3-42B9-81CA-6DB0A44E78A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB1C781-A986-4DA8-98BC-95E6B3CEC034}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{780FD12B-FE93-4AFF-99E8-C9A3B102E0A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{589A4D32-B194-4C15-9F03-651B5DA64FE2}"/>
 </file>